--- a/recipes/onion-garlic-free-indian/focus-states/08-meghalaya/excel/meghalaya-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/08-meghalaya/excel/meghalaya-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Boiled Veg with Sesame</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Boiled Veg with Sesame</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Side  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -1692,34 +1695,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Boil veg, toss with pounded sesame-chilli.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Boil veg, toss with pounded sesame-chilli. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 156  ·  Protein 5 g  ·  Carbs 20 g  ·  Fat 7 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Boiled Veg with Sesame: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1733,7 +1889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1745,7 +1901,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mustard Greens</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mustard Greens</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1755,7 +1911,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Side  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1775,44 +1931,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -1960,34 +2116,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Wilt in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Wilt in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 6  ·  Protein 0 g  ·  Carbs 1 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Mustard Greens: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2001,7 +2310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2013,7 +2322,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bean Stew</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bean Stew</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2023,7 +2332,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Side  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2043,44 +2352,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2228,34 +2537,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer until soft.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer until soft. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 219  ·  Protein 14 g  ·  Carbs 40 g  ·  Fat 1 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Bean Stew: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2269,7 +2731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2281,7 +2743,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Steamed Rice Cakes</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Steamed Rice Cakes</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2291,7 +2753,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Bread  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2311,44 +2773,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2478,33 +2940,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Shape cakes, steam 15 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Shape cakes, steam 15 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 135  ·  Protein 3 g  ·  Carbs 30 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Steamed Rice Cakes: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2518,7 +3133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2530,7 +3145,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sticky Rice</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sticky Rice</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2540,7 +3155,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Bread  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2560,44 +3175,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 5 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -2691,31 +3306,184 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="66" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Steam in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Steam in steel. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>kcal 360  ·  Protein 7 g  ·  Carbs 79 g  ·  Fat 1 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n"/>
+      <c r="C25" s="50" t="n"/>
+      <c r="D25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n"/>
+      <c r="C27" s="26" t="n"/>
+      <c r="D27" s="26" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="72" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>For Sticky Rice: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+    </row>
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="24">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2729,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2741,7 +3509,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Soft Roti</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Soft Roti</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2751,7 +3519,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Bread  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2771,44 +3539,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2920,32 +3688,185 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Iron tawa.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Iron tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 255  ·  Protein 9 g  ·  Carbs 54 g  ·  Fat 1 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Soft Roti: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2959,7 +3880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2971,7 +3892,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Minil Sesame Cake</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Minil Sesame Cake</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2981,7 +3902,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Sweet  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3001,44 +3922,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3168,33 +4089,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Fill, steam.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Fill, steam. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 265  ·  Protein 4 g  ·  Carbs 56 g  ·  Fat 3 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Minil Sesame Cake: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3208,7 +4282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3220,7 +4294,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pukhlein Sweet</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pukhlein Sweet</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3230,7 +4304,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Sweet  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3250,44 +4324,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -3417,33 +4491,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Fry sweeter, thicker discs.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Fry sweeter, thicker discs. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 212  ·  Protein 3 g  ·  Carbs 34 g  ·  Fat 7 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Pukhlein Sweet: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3457,7 +4684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3469,7 +4696,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Jaggery Rice</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Jaggery Rice</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3479,7 +4706,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Sweet  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3499,44 +4726,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3666,33 +4893,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Fold warm jaggery into rice.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Fold warm jaggery into rice. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 490  ·  Protein 8 g  ·  Carbs 105 g  ·  Fat 4 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Jaggery Rice: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3706,7 +5086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3718,7 +5098,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Red Rice Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Red Rice Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3728,7 +5108,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Dessert  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3748,44 +5128,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 10 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3933,34 +5313,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 436  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Red Rice Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4238,7 +5771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4250,7 +5783,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Milk Kheer</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Milk Kheer</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4260,7 +5793,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Dessert  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4280,44 +5813,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 10 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -4465,34 +5998,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Simmer in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Simmer in steel. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 437  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 9 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Milk Kheer: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4506,7 +6192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4518,7 +6204,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Banana Stew</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Banana Stew</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4528,7 +6214,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Dessert  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4548,44 +6234,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Prep 5 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -4733,34 +6419,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Stew gently in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Stew gently in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 504  ·  Protein 4 g  ·  Carbs 53 g  ·  Fat 33 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Banana Stew: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4774,7 +6613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4786,7 +6625,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Chilli Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Chilli Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4796,7 +6635,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Salad  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4816,44 +6655,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5001,34 +6840,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 16  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Chilli Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5042,7 +7034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5054,7 +7046,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Tomato Ginger Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Tomato Ginger Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5064,7 +7056,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Salad  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5084,44 +7076,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>6 min</t>
+          <t>Prep 6 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5269,34 +7261,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="54" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 14  ·  Protein 1 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Tomato Ginger Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5310,7 +7455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5322,7 +7467,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Green Papaya Salad</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Green Papaya Salad</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5332,7 +7477,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Salad  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5352,44 +7497,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -5555,35 +7700,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 112  ·  Protein 4 g  ·  Carbs 13 g  ·  Fat 6 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Green Papaya Salad: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7850,7 +10148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7862,7 +10160,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pukhlein</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pukhlein</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7872,7 +10170,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Starter  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7892,44 +10190,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -8077,34 +10375,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry discs in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry discs in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 293  ·  Protein 3 g  ·  Carbs 54 g  ·  Fat 7 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Pukhlein: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8118,7 +10569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8130,7 +10581,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Steamed Rice Puffs</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Steamed Rice Puffs</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8140,7 +10591,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Starter  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8160,44 +10611,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -8327,33 +10778,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Shape small cakes, steam.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Shape small cakes, steam. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 135  ·  Protein 3 g  ·  Carbs 30 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Steamed Rice Puffs: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8367,7 +10971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8379,7 +10983,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sesame Rice Balls</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sesame Rice Balls</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8389,7 +10993,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Starter  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8409,44 +11013,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -8576,33 +11180,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Steam balls.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Steam balls. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 169  ·  Protein 4 g  ·  Carbs 31 g  ·  Fat 3 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Sesame Rice Balls: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8616,7 +11373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8628,7 +11385,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Vegetarian Rice Pot</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Vegetarian Rice Pot</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,7 +11395,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Main  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8658,44 +11415,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -8897,37 +11654,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Temper ginger, chilli, tomato. Add rice, greens, water. Cook like a wet pulao.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Temper ginger, chilli, tomato. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Add rice, greens, water. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Cook like a wet pulao. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 346  ·  Protein 7 g  ·  Carbs 56 g  ·  Fat 10 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Vegetarian Rice Pot: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8941,7 +11877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8953,7 +11889,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Dal with Local Greens</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Dal with Local Greens</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8963,7 +11899,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Main  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8983,44 +11919,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 10 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -9204,36 +12140,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Cook dal, fold greens.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel or clay pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Wash greens in several changes of water; drain and squeeze dry.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook dal, fold greens. Work in Stainless steel or clay pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 226  ·  Protein 12 g  ·  Carbs 38 g  ·  Fat 4 g  ·  Fibre 8 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Dal with Local Greens: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9247,7 +12336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9259,7 +12348,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pumpkin Stew</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pumpkin Stew</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9269,7 +12358,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Meghalaya kitchen  ·  Main  ·  Khasi and Garo vegetarian home food</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Meghalaya  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9289,44 +12378,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -9492,35 +12581,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Simmer until the pumpkin collapses into a stew.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Simmer until the pumpkin collapses into a stew. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 59  ·  Protein 2 g  ·  Carbs 8 g  ·  Fat 3 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Sesame · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Pumpkin Stew: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Sesame; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
